--- a/МО 19.10.2026/Сверка со штаткой 19.10.2026 — протокол.xlsx
+++ b/МО 19.10.2026/Сверка со штаткой 19.10.2026 — протокол.xlsx
@@ -492,7 +492,7 @@
         <v>331</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4">
@@ -505,7 +505,7 @@
         <v>165</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
@@ -518,7 +518,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>223 + 5</t>
+          <t>218 + 5</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Нет даты предварительного осмотра — включён в список ПМО 2026 по общему правилу; при наличии заключения предварительного осмотра — исключить</t>
+          <t>Предварительный осмотр 01.10.2026 (по данным ОТиПБ); следующий — 01.10.2027, в список ПМО 2026 не включён</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Нет даты предварительного осмотра — включён в список ПМО 2026 по общему правилу; при наличии заключения предварительного осмотра — исключить</t>
+          <t>Предварительный осмотр 01.10.2026 (по данным ОТиПБ); следующий — 01.10.2027, в список ПМО 2026 не включён</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Нет даты предварительного осмотра — включён в список ПМО 2026 по общему правилу; при наличии заключения предварительного осмотра — исключить</t>
+          <t>Предварительный осмотр 01.10.2026 (по данным ОТиПБ); следующий — 01.10.2027, в список ПМО 2026 не включён</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Нет даты предварительного осмотра — включён в список ПМО 2026 по общему правилу; при наличии заключения предварительного осмотра — исключить</t>
+          <t>Предварительный осмотр 01.10.2026 (по данным ОТиПБ); следующий — 01.10.2027, в список ПМО 2026 не включён</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Нет даты предварительного осмотра — включён в список ПМО 2026 по общему правилу; при наличии заключения предварительного осмотра — исключить</t>
+          <t>Предварительный осмотр 01.10.2026 (по данным ОТиПБ); следующий — 01.10.2027, в список ПМО 2026 не включён</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Нет даты предварительного осмотра — включён в список ПМО 2026 по общему правилу; при наличии заключения предварительного осмотра — исключить</t>
+          <t>Предварительный осмотр 01.10.2026 (по данным ОТиПБ); следующий — 01.10.2027, в список ПМО 2026 не включён</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4938,34 +4938,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Новые работники</t>
+          <t>Пункты в прежней редакции приказа о ПМО</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>6 чел. без даты предварительного осмотра включены в список ПМО 2026 (как ранее Власова О.В., Ефременко Р.В.). Запросить у отдела кадров заключения предварительных осмотров; при их наличии исключить из ПМО 2026.</t>
+          <t>Прежний приказ расходился с шаблоном: уборщикам (10 чел.) не указан п.4.3.1; 30 ИТР и служащим не указан п.5.1; водителям вместо п.18 указаны 18.1/18.2; операторам склада и кладовщикам-комплектовщикам — пункты до изменения 19.10.2026. В новой редакции пункты взяты точно из шаблона. Если сокращения были решением ОТиПБ — внести их в Приказ №43 и журнал.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Пункты в прежней редакции приказа о ПМО</t>
+          <t>п.18 для водителей-экспедиторов</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Прежний приказ расходился с шаблоном: уборщикам (10 чел.) не указан п.4.3.1; 30 ИТР и служащим не указан п.5.1; водителям вместо п.18 указаны 18.1/18.2; операторам склада и кладовщикам-комплектовщикам — пункты до изменения 19.10.2026. В новой редакции пункты взяты точно из шаблона. Если сокращения были решением ОТиПБ — внести их в Приказ №43 и журнал.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>п.18 для водителей-экспедиторов</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>В Перечне и шаблоне указан «п.18» без подпункта. Медорганизации нужен подпункт (18.1 — кат. B, 18.2 — кат. C и выше). Уточнить по категориям водительских удостоверений.</t>
         </is>

--- a/МО 19.10.2026/Сверка со штаткой 19.10.2026 — протокол.xlsx
+++ b/МО 19.10.2026/Сверка со штаткой 19.10.2026 — протокол.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Добавлены" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Изменения" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Не включены" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Решения" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4880,7 +4881,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Тема</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Решение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Гришин Алексей Валерьевич (Руднево), перевод с новым фактором п.4.3.2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Осмотр нужен (решение ОТиПБ, 19.10.2026). Проводится в выездном ПМО 28.10.2026 по пунктам новой должности: п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15. Включён в список ПМО, шаблон ЛМК и Приложение № 1 к приказу о ПМО (№ 25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Новые работники (6 чел.)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Предварительный осмотр 01.10.2026; в ПМО 2026 не включены.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4926,34 +4981,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Перевод с новым фактором</t>
+          <t>Пункты в прежней редакции приказа о ПМО</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Гришин Алексей Валерьевич (Руднево): слесарь-ремонтник → слесарь механосборочных работ, добавился п.4.3.2. Нужен ли осмотр при переводе — решить.</t>
+          <t>Прежний приказ расходился с шаблоном: уборщикам (10 чел.) не указан п.4.3.1; 30 ИТР и служащим не указан п.5.1; водителям вместо п.18 указаны 18.1/18.2; операторам склада и кладовщикам-комплектовщикам — пункты до изменения 19.10.2026. В новой редакции пункты взяты точно из шаблона. Если сокращения были решением ОТиПБ — внести их в Приказ №43 и журнал.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Пункты в прежней редакции приказа о ПМО</t>
+          <t>п.18 для водителей-экспедиторов</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Прежний приказ расходился с шаблоном: уборщикам (10 чел.) не указан п.4.3.1; 30 ИТР и служащим не указан п.5.1; водителям вместо п.18 указаны 18.1/18.2; операторам склада и кладовщикам-комплектовщикам — пункты до изменения 19.10.2026. В новой редакции пункты взяты точно из шаблона. Если сокращения были решением ОТиПБ — внести их в Приказ №43 и журнал.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>п.18 для водителей-экспедиторов</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>В Перечне и шаблоне указан «п.18» без подпункта. Медорганизации нужен подпункт (18.1 — кат. B, 18.2 — кат. C и выше). Уточнить по категориям водительских удостоверений.</t>
         </is>

--- a/МО 19.10.2026/Сверка со штаткой 19.10.2026 — протокол.xlsx
+++ b/МО 19.10.2026/Сверка со штаткой 19.10.2026 — протокол.xlsx
@@ -4881,7 +4881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4921,6 +4921,18 @@
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Предварительный осмотр 01.10.2026; в ПМО 2026 не включены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Пункты 29н (решение ОТиПБ)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Уборщики — п.1.48, п.4.4, п.5.1; специалист, инженер и контролер ОТК, мастер участка, должности ПДО — п.4.4, п.5.2; бригадир — п.4.4, п.5.1, п.5.2 (отдельная позиция п.47); водители-экспедиторы — п.18.1 (Батуревич, Василенко, Евдокимов, Ерофеев, Крутяков, Лучкин) или п.18.2 (Акимов, Грязнов, Жигунов). Внесено в «Перечень» журнала; требуется внести в Приказ №43.</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4978,30 +4990,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Пункты в прежней редакции приказа о ПМО</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Прежний приказ расходился с шаблоном: уборщикам (10 чел.) не указан п.4.3.1; 30 ИТР и служащим не указан п.5.1; водителям вместо п.18 указаны 18.1/18.2; операторам склада и кладовщикам-комплектовщикам — пункты до изменения 19.10.2026. В новой редакции пункты взяты точно из шаблона. Если сокращения были решением ОТиПБ — внести их в Приказ №43 и журнал.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>п.18 для водителей-экспедиторов</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>В Перечне и шаблоне указан «п.18» без подпункта. Медорганизации нужен подпункт (18.1 — кат. B, 18.2 — кат. C и выше). Уточнить по категориям водительских удостоверений.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
